--- a/results/Int Task Remove ACC -0.9/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_10_permute.xlsx
@@ -440,177 +440,177 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6639032914616432</v>
+        <v>0.6719478863750714</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6608272288218222</v>
+        <v>0.6392333188360069</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6563344789063899</v>
+        <v>0.6403383846567119</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6565000611161804</v>
+        <v>0.6403383846567119</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6569698029216378</v>
+        <v>0.6414054305279586</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6549362686155622</v>
+        <v>0.6346449860569829</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6568422406613055</v>
+        <v>0.6448751950743201</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.665459622103022</v>
+        <v>0.6167429197615617</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6674931564090976</v>
+        <v>0.6233487971482906</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6597036860163337</v>
+        <v>0.6196889328546373</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6611754489196648</v>
+        <v>0.6228570250917453</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6562559517210601</v>
+        <v>0.6232887469477442</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6459521900912195</v>
+        <v>0.6189015290415562</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6457350855200135</v>
+        <v>0.6399077287806043</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6535380583247344</v>
+        <v>0.6461383812455762</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5862423924568421</v>
+        <v>0.6449437731139973</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5884574986710784</v>
+        <v>0.648323995349485</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.590287430817905</v>
+        <v>0.633617026115086</v>
       </c>
     </row>
     <row r="20">
@@ -620,707 +620,707 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5932089263734796</v>
+        <v>0.6331607867215859</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5914550341255695</v>
+        <v>0.6329817020998383</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6177033676436727</v>
+        <v>0.6141415735000242</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6176273277447561</v>
+        <v>0.6388996671300127</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6223997197183539</v>
+        <v>0.637857138796267</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6203551702867344</v>
+        <v>0.639725090892552</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6203551702867344</v>
+        <v>0.6273142423441325</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6096196868008948</v>
+        <v>0.6273142423441325</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6004860157651319</v>
+        <v>0.6152405987680115</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5909646833755462</v>
+        <v>0.6291342253453065</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6037877108152898</v>
+        <v>0.6173562135257213</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6046646569392449</v>
+        <v>0.6366440536799047</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6084385810812731</v>
+        <v>0.6335054535531242</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5985310086443862</v>
+        <v>0.6024445761521822</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5607118187322514</v>
+        <v>0.5345981540070894</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5607118187322514</v>
+        <v>0.5345981540070894</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5419893032471169</v>
+        <v>0.5320433555341413</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5669215069260267</v>
+        <v>0.547315649437589</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5784493687977736</v>
+        <v>0.5782528731711338</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5709285253376314</v>
+        <v>0.5758881744454772</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5709285253376314</v>
+        <v>0.5471109812984488</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5575781931782973</v>
+        <v>0.6327304861721088</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5436291356466518</v>
+        <v>0.6327304861721088</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5664052173319802</v>
+        <v>0.6573635048281783</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5619003863111126</v>
+        <v>0.6599318057130836</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5445515635793047</v>
+        <v>0.6643740992469918</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5490933485697392</v>
+        <v>0.6720996108462743</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5492969507289881</v>
+        <v>0.6554180915264548</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5502879567013181</v>
+        <v>0.6146702995261364</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5653406587471468</v>
+        <v>0.6055167301990683</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5697609220299669</v>
+        <v>0.6152526798734469</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5695192999212596</v>
+        <v>0.5828387186637445</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6216794726384282</v>
+        <v>0.5980889823161042</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6590740472271731</v>
+        <v>0.5837341417724828</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6587944051690076</v>
+        <v>0.5793359087407508</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5984130402030763</v>
+        <v>0.5857566609530145</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6131615826532382</v>
+        <v>0.5673422136564816</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5583041254843102</v>
+        <v>0.5413600197845868</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5623957116339624</v>
+        <v>0.6426096324785596</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.566424760296655</v>
+        <v>0.6122867684890659</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5668564821526541</v>
+        <v>0.6273064251582625</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5542505592841163</v>
+        <v>0.6164579478039393</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5460673869848118</v>
+        <v>0.6282899692713529</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5450763810124819</v>
+        <v>0.6389160121550134</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5390702949779556</v>
+        <v>0.6190393957741714</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5443294844352723</v>
+        <v>0.5865824400421844</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5952694655034694</v>
+        <v>0.5822982668588272</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5190252537742794</v>
+        <v>0.5499223255985832</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5088110344553127</v>
+        <v>0.5507097294116644</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5119926291043779</v>
+        <v>0.5566447501201004</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5483361475202465</v>
+        <v>0.5451659233233558</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5483361475202465</v>
+        <v>0.5451659233233558</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5486722865126539</v>
+        <v>0.5451659233233558</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5225511599282524</v>
+        <v>0.5398527242182104</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5362696104767346</v>
+        <v>0.5378952298110515</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5403096742649713</v>
+        <v>0.5506582070502488</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.57780942553633</v>
+        <v>0.5596692903985059</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.562896366856269</v>
+        <v>0.5342328782309851</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5614956692790281</v>
+        <v>0.5348682022462328</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5614956692790281</v>
+        <v>0.5348682022462328</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5642270650873109</v>
+        <v>0.5139195654213179</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5661330371330542</v>
+        <v>0.5116689265440363</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4682405504435898</v>
+        <v>0.5055168012643942</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4689654167697114</v>
+        <v>0.5078434800405925</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4795953682463067</v>
+        <v>0.5061411101540981</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.469576223247458</v>
+        <v>0.5088860083743381</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5308423515232142</v>
+        <v>0.5115843588059888</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5271935023551049</v>
+        <v>0.5084567738047523</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5194885997003886</v>
+        <v>0.5091301177694584</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5037732134887675</v>
+        <v>0.5082531716455034</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5037732134887675</v>
+        <v>0.5040585407730203</v>
       </c>
     </row>
   </sheetData>
